--- a/Dashboards/data/Data final/pobreza/series_historicas_indicadores.xlsx
+++ b/Dashboards/data/Data final/pobreza/series_historicas_indicadores.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="47" uniqueCount="5">
   <si>
     <t>anio</t>
   </si>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -125,7 +125,7 @@
         <v>2003</v>
       </c>
       <c r="B5" s="1">
-        <v>30.821599960327148</v>
+        <v>30.821599960327149</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -202,7 +202,7 @@
         <v>2009</v>
       </c>
       <c r="B12" s="1">
-        <v>36.026199340820312</v>
+        <v>36.026199340820313</v>
       </c>
       <c r="C12" t="s">
         <v>3</v>
@@ -378,7 +378,7 @@
         <v>2017</v>
       </c>
       <c r="B28" s="1">
-        <v>21.480300903320312</v>
+        <v>21.480300903320313</v>
       </c>
       <c r="C28" t="s">
         <v>3</v>
@@ -488,7 +488,7 @@
         <v>2022</v>
       </c>
       <c r="B38" s="1">
-        <v>25.227300643920898</v>
+        <v>25.227300643920899</v>
       </c>
       <c r="C38" t="s">
         <v>3</v>
